--- a/excel/flashcards_master.xlsx
+++ b/excel/flashcards_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrmath3/Documents/GitHub/flashcards/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrmath3/Documents/GitHub/mr-sindel-math/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AFA652-6A39-A445-80B7-9A069344B7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42A9ABFE-341E-2C47-AEBF-DD0838AA60A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{DB8C5BD4-B13A-AA46-9C13-196CEA47E358}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{DB8C5BD4-B13A-AA46-9C13-196CEA47E358}"/>
   </bookViews>
   <sheets>
     <sheet name="cards_master" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="166">
   <si>
     <t>deck</t>
   </si>
@@ -75,12 +75,6 @@
     <t>$-\frac{1}{2}$</t>
   </si>
   <si>
-    <t>$\cos(0)$</t>
-  </si>
-  <si>
-    <t>$\cos\left(\frac{\pi}{6}\right)$</t>
-  </si>
-  <si>
     <t>$\cos\left(\frac{\pi}{4}\right)$</t>
   </si>
   <si>
@@ -297,13 +291,253 @@
     <t>trig values sin cos radians</t>
   </si>
   <si>
-    <t>trig values tan radians</t>
-  </si>
-  <si>
-    <t>tan_rad_01</t>
-  </si>
-  <si>
-    <t>tan_rad_02</t>
+    <t>\cos(0)</t>
+  </si>
+  <si>
+    <t>\cos\left(\frac{\pi}{6}\right)</t>
+  </si>
+  <si>
+    <t>1^2</t>
+  </si>
+  <si>
+    <t>2^2</t>
+  </si>
+  <si>
+    <t>3^2</t>
+  </si>
+  <si>
+    <t>4^2</t>
+  </si>
+  <si>
+    <t>5^2</t>
+  </si>
+  <si>
+    <t>6^2</t>
+  </si>
+  <si>
+    <t>7^2</t>
+  </si>
+  <si>
+    <t>8^2</t>
+  </si>
+  <si>
+    <t>9^2</t>
+  </si>
+  <si>
+    <t>10^2</t>
+  </si>
+  <si>
+    <t>11^2</t>
+  </si>
+  <si>
+    <t>12^2</t>
+  </si>
+  <si>
+    <t>13^2</t>
+  </si>
+  <si>
+    <t>14^2</t>
+  </si>
+  <si>
+    <t>15^2</t>
+  </si>
+  <si>
+    <t>16^2</t>
+  </si>
+  <si>
+    <t>17^2</t>
+  </si>
+  <si>
+    <t>18^2</t>
+  </si>
+  <si>
+    <t>19^2</t>
+  </si>
+  <si>
+    <t>20^2</t>
+  </si>
+  <si>
+    <t>sqrt(1)</t>
+  </si>
+  <si>
+    <t>sqrt(4)</t>
+  </si>
+  <si>
+    <t>sqrt(9)</t>
+  </si>
+  <si>
+    <t>sqrt(16)</t>
+  </si>
+  <si>
+    <t>sqrt(25)</t>
+  </si>
+  <si>
+    <t>sqrt(36)</t>
+  </si>
+  <si>
+    <t>sqrt(49)</t>
+  </si>
+  <si>
+    <t>sqrt(64)</t>
+  </si>
+  <si>
+    <t>sqrt(81)</t>
+  </si>
+  <si>
+    <t>sqrt(100)</t>
+  </si>
+  <si>
+    <t>sqrt(121)</t>
+  </si>
+  <si>
+    <t>sqrt(144)</t>
+  </si>
+  <si>
+    <t>sqrt(169)</t>
+  </si>
+  <si>
+    <t>sqrt(196)</t>
+  </si>
+  <si>
+    <t>sqrt(225)</t>
+  </si>
+  <si>
+    <t>sqrt(256)</t>
+  </si>
+  <si>
+    <t>sqrt(289)</t>
+  </si>
+  <si>
+    <t>sqrt(324)</t>
+  </si>
+  <si>
+    <t>sqrt(361)</t>
+  </si>
+  <si>
+    <t>sqrt(400)</t>
+  </si>
+  <si>
+    <t>square_1</t>
+  </si>
+  <si>
+    <t>square_2</t>
+  </si>
+  <si>
+    <t>square_3</t>
+  </si>
+  <si>
+    <t>square_4</t>
+  </si>
+  <si>
+    <t>square_5</t>
+  </si>
+  <si>
+    <t>square_6</t>
+  </si>
+  <si>
+    <t>square_7</t>
+  </si>
+  <si>
+    <t>square_8</t>
+  </si>
+  <si>
+    <t>square_9</t>
+  </si>
+  <si>
+    <t>square_10</t>
+  </si>
+  <si>
+    <t>square_11</t>
+  </si>
+  <si>
+    <t>square_12</t>
+  </si>
+  <si>
+    <t>square_13</t>
+  </si>
+  <si>
+    <t>square_14</t>
+  </si>
+  <si>
+    <t>square_15</t>
+  </si>
+  <si>
+    <t>square_16</t>
+  </si>
+  <si>
+    <t>square_17</t>
+  </si>
+  <si>
+    <t>square_18</t>
+  </si>
+  <si>
+    <t>square_19</t>
+  </si>
+  <si>
+    <t>square_20</t>
+  </si>
+  <si>
+    <t>sqrt_1</t>
+  </si>
+  <si>
+    <t>sqrt_2</t>
+  </si>
+  <si>
+    <t>sqrt_3</t>
+  </si>
+  <si>
+    <t>sqrt_4</t>
+  </si>
+  <si>
+    <t>sqrt_5</t>
+  </si>
+  <si>
+    <t>sqrt_6</t>
+  </si>
+  <si>
+    <t>sqrt_7</t>
+  </si>
+  <si>
+    <t>sqrt_8</t>
+  </si>
+  <si>
+    <t>sqrt_9</t>
+  </si>
+  <si>
+    <t>sqrt_10</t>
+  </si>
+  <si>
+    <t>sqrt_11</t>
+  </si>
+  <si>
+    <t>sqrt_12</t>
+  </si>
+  <si>
+    <t>sqrt_13</t>
+  </si>
+  <si>
+    <t>sqrt_14</t>
+  </si>
+  <si>
+    <t>sqrt_15</t>
+  </si>
+  <si>
+    <t>sqrt_16</t>
+  </si>
+  <si>
+    <t>sqrt_17</t>
+  </si>
+  <si>
+    <t>sqrt_18</t>
+  </si>
+  <si>
+    <t>sqrt_19</t>
+  </si>
+  <si>
+    <t>sqrt_20</t>
+  </si>
+  <si>
+    <t>squares and square roots</t>
   </si>
 </sst>
 </file>
@@ -688,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41C7E2C-9CA0-AA49-8CE9-EFA3FDD48945}">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="7" width="37" customWidth="1"/>
@@ -713,7 +947,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -736,13 +970,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
@@ -759,68 +993,68 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>10</v>
@@ -828,13 +1062,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -851,22 +1085,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>9</v>
@@ -874,59 +1108,59 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>8</v>
@@ -943,68 +1177,68 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>9</v>
@@ -1012,13 +1246,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>7</v>
@@ -1035,22 +1269,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>10</v>
@@ -1058,59 +1292,59 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>6</v>
@@ -1127,13 +1361,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>7</v>
@@ -1150,22 +1384,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>10</v>
@@ -1173,59 +1407,59 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>6</v>
@@ -1242,68 +1476,68 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>10</v>
@@ -1311,13 +1545,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>7</v>
@@ -1334,22 +1568,22 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>9</v>
@@ -1357,59 +1591,59 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>8</v>
@@ -1426,68 +1660,68 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>9</v>
@@ -1495,13 +1729,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>7</v>
@@ -1518,15 +1752,922 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>85</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36">
+        <v>9</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>9</v>
+      </c>
+      <c r="G37">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" t="s">
+        <v>165</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>87</v>
+      </c>
+      <c r="D38">
+        <v>9</v>
+      </c>
+      <c r="E38">
+        <v>16</v>
+      </c>
+      <c r="F38">
+        <v>6</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" t="s">
+        <v>165</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39">
+        <v>16</v>
+      </c>
+      <c r="E39">
+        <v>9</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
+        <v>165</v>
+      </c>
+      <c r="C40" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40">
+        <v>25</v>
+      </c>
+      <c r="E40">
+        <v>9</v>
+      </c>
+      <c r="F40">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" t="s">
+        <v>165</v>
+      </c>
+      <c r="C41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41">
+        <v>36</v>
+      </c>
+      <c r="E41">
+        <v>34</v>
+      </c>
+      <c r="F41">
+        <v>38</v>
+      </c>
+      <c r="G41">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>165</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42">
+        <v>49</v>
+      </c>
+      <c r="E42">
+        <v>52</v>
+      </c>
+      <c r="F42">
+        <v>51</v>
+      </c>
+      <c r="G42">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43">
+        <v>64</v>
+      </c>
+      <c r="E43">
+        <v>36</v>
+      </c>
+      <c r="F43">
+        <v>62</v>
+      </c>
+      <c r="G43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44">
+        <v>81</v>
+      </c>
+      <c r="E44">
+        <v>49</v>
+      </c>
+      <c r="F44">
+        <v>84</v>
+      </c>
+      <c r="G44">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45">
+        <v>100</v>
+      </c>
+      <c r="E45">
+        <v>101</v>
+      </c>
+      <c r="F45">
+        <v>81</v>
+      </c>
+      <c r="G45">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" t="s">
+        <v>165</v>
+      </c>
+      <c r="C46" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46">
+        <v>121</v>
+      </c>
+      <c r="E46">
+        <v>100</v>
+      </c>
+      <c r="F46">
+        <v>122</v>
+      </c>
+      <c r="G46">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" t="s">
+        <v>165</v>
+      </c>
+      <c r="C47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47">
+        <v>144</v>
+      </c>
+      <c r="E47">
+        <v>169</v>
+      </c>
+      <c r="F47">
+        <v>121</v>
+      </c>
+      <c r="G47">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>137</v>
+      </c>
+      <c r="B48" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48">
+        <v>169</v>
+      </c>
+      <c r="E48">
+        <v>121</v>
+      </c>
+      <c r="F48">
+        <v>172</v>
+      </c>
+      <c r="G48">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" t="s">
+        <v>165</v>
+      </c>
+      <c r="C49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49">
+        <v>196</v>
+      </c>
+      <c r="E49">
+        <v>256</v>
+      </c>
+      <c r="F49">
+        <v>195</v>
+      </c>
+      <c r="G49">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50">
+        <v>225</v>
+      </c>
+      <c r="E50">
+        <v>256</v>
+      </c>
+      <c r="F50">
+        <v>196</v>
+      </c>
+      <c r="G50">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51">
+        <v>256</v>
+      </c>
+      <c r="E51">
+        <v>253</v>
+      </c>
+      <c r="F51">
+        <v>257</v>
+      </c>
+      <c r="G51">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" t="s">
+        <v>165</v>
+      </c>
+      <c r="C52" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52">
+        <v>289</v>
+      </c>
+      <c r="E52">
+        <v>324</v>
+      </c>
+      <c r="F52">
+        <v>361</v>
+      </c>
+      <c r="G52">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>142</v>
+      </c>
+      <c r="B53" t="s">
+        <v>165</v>
+      </c>
+      <c r="C53" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53">
+        <v>324</v>
+      </c>
+      <c r="E53">
+        <v>326</v>
+      </c>
+      <c r="F53">
+        <v>289</v>
+      </c>
+      <c r="G53">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" t="s">
+        <v>103</v>
+      </c>
+      <c r="D54">
+        <v>361</v>
+      </c>
+      <c r="E54">
+        <v>364</v>
+      </c>
+      <c r="F54">
+        <v>400</v>
+      </c>
+      <c r="G54">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" t="s">
+        <v>165</v>
+      </c>
+      <c r="C55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55">
+        <v>400</v>
+      </c>
+      <c r="E55">
+        <v>361</v>
+      </c>
+      <c r="F55">
+        <v>397</v>
+      </c>
+      <c r="G55">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" t="s">
+        <v>165</v>
+      </c>
+      <c r="C56" t="s">
+        <v>105</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" t="s">
+        <v>165</v>
+      </c>
+      <c r="C58" t="s">
+        <v>107</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>148</v>
+      </c>
+      <c r="B59" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" t="s">
+        <v>108</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59">
+        <v>5</v>
+      </c>
+      <c r="F59">
+        <v>8</v>
+      </c>
+      <c r="G59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" t="s">
+        <v>109</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60">
+        <v>4</v>
+      </c>
+      <c r="F60">
+        <v>6</v>
+      </c>
+      <c r="G60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" t="s">
+        <v>165</v>
+      </c>
+      <c r="C61" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61">
+        <v>6</v>
+      </c>
+      <c r="E61">
+        <v>8</v>
+      </c>
+      <c r="F61">
+        <v>5</v>
+      </c>
+      <c r="G61">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>151</v>
+      </c>
+      <c r="B62" t="s">
+        <v>165</v>
+      </c>
+      <c r="C62" t="s">
+        <v>111</v>
+      </c>
+      <c r="D62">
+        <v>7</v>
+      </c>
+      <c r="E62">
+        <v>6</v>
+      </c>
+      <c r="F62">
+        <v>8</v>
+      </c>
+      <c r="G62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" t="s">
+        <v>165</v>
+      </c>
+      <c r="C63" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63">
+        <v>8</v>
+      </c>
+      <c r="E63">
+        <v>9</v>
+      </c>
+      <c r="F63">
+        <v>7</v>
+      </c>
+      <c r="G63">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>153</v>
+      </c>
+      <c r="B64" t="s">
+        <v>165</v>
+      </c>
+      <c r="C64" t="s">
+        <v>113</v>
+      </c>
+      <c r="D64">
+        <v>9</v>
+      </c>
+      <c r="E64">
+        <v>8</v>
+      </c>
+      <c r="F64">
+        <v>10</v>
+      </c>
+      <c r="G64">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s">
+        <v>165</v>
+      </c>
+      <c r="C65" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65">
+        <v>10</v>
+      </c>
+      <c r="E65">
+        <v>9</v>
+      </c>
+      <c r="F65">
+        <v>11</v>
+      </c>
+      <c r="G65">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" t="s">
+        <v>165</v>
+      </c>
+      <c r="C66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66">
+        <v>11</v>
+      </c>
+      <c r="E66">
+        <v>12</v>
+      </c>
+      <c r="F66">
+        <v>13</v>
+      </c>
+      <c r="G66">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>156</v>
+      </c>
+      <c r="B67" t="s">
+        <v>165</v>
+      </c>
+      <c r="C67" t="s">
+        <v>116</v>
+      </c>
+      <c r="D67">
+        <v>12</v>
+      </c>
+      <c r="E67">
+        <v>14</v>
+      </c>
+      <c r="F67">
+        <v>10</v>
+      </c>
+      <c r="G67">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>157</v>
+      </c>
+      <c r="B68" t="s">
+        <v>165</v>
+      </c>
+      <c r="C68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D68">
+        <v>13</v>
+      </c>
+      <c r="E68">
+        <v>12</v>
+      </c>
+      <c r="F68">
+        <v>14</v>
+      </c>
+      <c r="G68">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" t="s">
+        <v>165</v>
+      </c>
+      <c r="C69" t="s">
+        <v>118</v>
+      </c>
+      <c r="D69">
+        <v>14</v>
+      </c>
+      <c r="E69">
+        <v>15</v>
+      </c>
+      <c r="F69">
+        <v>13</v>
+      </c>
+      <c r="G69">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" t="s">
+        <v>165</v>
+      </c>
+      <c r="C70" t="s">
+        <v>119</v>
+      </c>
+      <c r="D70">
+        <v>15</v>
+      </c>
+      <c r="E70">
+        <v>17</v>
+      </c>
+      <c r="F70">
+        <v>14</v>
+      </c>
+      <c r="G70">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71" t="s">
+        <v>120</v>
+      </c>
+      <c r="D71">
+        <v>16</v>
+      </c>
+      <c r="E71">
+        <v>17</v>
+      </c>
+      <c r="F71">
+        <v>18</v>
+      </c>
+      <c r="G71">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>161</v>
+      </c>
+      <c r="B72" t="s">
+        <v>165</v>
+      </c>
+      <c r="C72" t="s">
+        <v>121</v>
+      </c>
+      <c r="D72">
+        <v>17</v>
+      </c>
+      <c r="E72">
+        <v>15</v>
+      </c>
+      <c r="F72">
+        <v>16</v>
+      </c>
+      <c r="G72">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" t="s">
+        <v>165</v>
+      </c>
+      <c r="C73" t="s">
+        <v>122</v>
+      </c>
+      <c r="D73">
+        <v>18</v>
+      </c>
+      <c r="E73">
+        <v>19</v>
+      </c>
+      <c r="F73">
+        <v>17</v>
+      </c>
+      <c r="G73">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C74" t="s">
+        <v>123</v>
+      </c>
+      <c r="D74">
+        <v>19</v>
+      </c>
+      <c r="E74">
+        <v>18</v>
+      </c>
+      <c r="F74">
+        <v>20</v>
+      </c>
+      <c r="G74">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>164</v>
+      </c>
+      <c r="B75" t="s">
+        <v>165</v>
+      </c>
+      <c r="C75" t="s">
+        <v>124</v>
+      </c>
+      <c r="D75">
+        <v>20</v>
+      </c>
+      <c r="E75">
+        <v>22</v>
+      </c>
+      <c r="F75">
+        <v>19</v>
+      </c>
+      <c r="G75">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1538,7 +2679,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2891CE-84D5-EF44-9F8F-0E7C3321DDFA}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
@@ -2156,6 +3297,566 @@
 SUBSTITUTE(SUBSTITUTE(cards_master!D35,"$",""),"\sqrt{3}","\sqrt3") &amp;
 " }}\)"</f>
         <v>\(\sin(2\pi)={{c1::0 }}\)</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f>cards_master!A36</f>
+        <v>square_1</v>
+      </c>
+      <c r="B35" t="str">
+        <f>cards_master!B36</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C35" t="str">
+        <f>"\("&amp;cards_master!C36&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D36&amp;"\)}}"</f>
+        <v>\(1^2\) = {{c1::\(1\)}}</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
+        <f>cards_master!A37</f>
+        <v>square_2</v>
+      </c>
+      <c r="B36" t="str">
+        <f>cards_master!B37</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C36" t="str">
+        <f>"\("&amp;cards_master!C37&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D37&amp;"\)}}"</f>
+        <v>\(2^2\) = {{c1::\(4\)}}</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="str">
+        <f>cards_master!A38</f>
+        <v>square_3</v>
+      </c>
+      <c r="B37" t="str">
+        <f>cards_master!B38</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C37" t="str">
+        <f>"\("&amp;cards_master!C38&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D38&amp;"\)}}"</f>
+        <v>\(3^2\) = {{c1::\(9\)}}</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="str">
+        <f>cards_master!A39</f>
+        <v>square_4</v>
+      </c>
+      <c r="B38" t="str">
+        <f>cards_master!B39</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C38" t="str">
+        <f>"\("&amp;cards_master!C39&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D39&amp;"\)}}"</f>
+        <v>\(4^2\) = {{c1::\(16\)}}</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="str">
+        <f>cards_master!A40</f>
+        <v>square_5</v>
+      </c>
+      <c r="B39" t="str">
+        <f>cards_master!B40</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C39" t="str">
+        <f>"\("&amp;cards_master!C40&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D40&amp;"\)}}"</f>
+        <v>\(5^2\) = {{c1::\(25\)}}</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="str">
+        <f>cards_master!A41</f>
+        <v>square_6</v>
+      </c>
+      <c r="B40" t="str">
+        <f>cards_master!B41</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C40" t="str">
+        <f>"\("&amp;cards_master!C41&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D41&amp;"\)}}"</f>
+        <v>\(6^2\) = {{c1::\(36\)}}</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="str">
+        <f>cards_master!A42</f>
+        <v>square_7</v>
+      </c>
+      <c r="B41" t="str">
+        <f>cards_master!B42</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C41" t="str">
+        <f>"\("&amp;cards_master!C42&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D42&amp;"\)}}"</f>
+        <v>\(7^2\) = {{c1::\(49\)}}</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>cards_master!A43</f>
+        <v>square_8</v>
+      </c>
+      <c r="B42" t="str">
+        <f>cards_master!B43</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C42" t="str">
+        <f>"\("&amp;cards_master!C43&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D43&amp;"\)}}"</f>
+        <v>\(8^2\) = {{c1::\(64\)}}</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>cards_master!A44</f>
+        <v>square_9</v>
+      </c>
+      <c r="B43" t="str">
+        <f>cards_master!B44</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C43" t="str">
+        <f>"\("&amp;cards_master!C44&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D44&amp;"\)}}"</f>
+        <v>\(9^2\) = {{c1::\(81\)}}</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f>cards_master!A45</f>
+        <v>square_10</v>
+      </c>
+      <c r="B44" t="str">
+        <f>cards_master!B45</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C44" t="str">
+        <f>"\("&amp;cards_master!C45&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D45&amp;"\)}}"</f>
+        <v>\(10^2\) = {{c1::\(100\)}}</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>cards_master!A46</f>
+        <v>square_11</v>
+      </c>
+      <c r="B45" t="str">
+        <f>cards_master!B46</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C45" t="str">
+        <f>"\("&amp;cards_master!C46&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D46&amp;"\)}}"</f>
+        <v>\(11^2\) = {{c1::\(121\)}}</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>cards_master!A47</f>
+        <v>square_12</v>
+      </c>
+      <c r="B46" t="str">
+        <f>cards_master!B47</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C46" t="str">
+        <f>"\("&amp;cards_master!C47&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D47&amp;"\)}}"</f>
+        <v>\(12^2\) = {{c1::\(144\)}}</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="str">
+        <f>cards_master!A48</f>
+        <v>square_13</v>
+      </c>
+      <c r="B47" t="str">
+        <f>cards_master!B48</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C47" t="str">
+        <f>"\("&amp;cards_master!C48&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D48&amp;"\)}}"</f>
+        <v>\(13^2\) = {{c1::\(169\)}}</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" t="str">
+        <f>cards_master!A49</f>
+        <v>square_14</v>
+      </c>
+      <c r="B48" t="str">
+        <f>cards_master!B49</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C48" t="str">
+        <f>"\("&amp;cards_master!C49&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D49&amp;"\)}}"</f>
+        <v>\(14^2\) = {{c1::\(196\)}}</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" t="str">
+        <f>cards_master!A50</f>
+        <v>square_15</v>
+      </c>
+      <c r="B49" t="str">
+        <f>cards_master!B50</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C49" t="str">
+        <f>"\("&amp;cards_master!C50&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D50&amp;"\)}}"</f>
+        <v>\(15^2\) = {{c1::\(225\)}}</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" t="str">
+        <f>cards_master!A51</f>
+        <v>square_16</v>
+      </c>
+      <c r="B50" t="str">
+        <f>cards_master!B51</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C50" t="str">
+        <f>"\("&amp;cards_master!C51&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D51&amp;"\)}}"</f>
+        <v>\(16^2\) = {{c1::\(256\)}}</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="str">
+        <f>cards_master!A52</f>
+        <v>square_17</v>
+      </c>
+      <c r="B51" t="str">
+        <f>cards_master!B52</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C51" t="str">
+        <f>"\("&amp;cards_master!C52&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D52&amp;"\)}}"</f>
+        <v>\(17^2\) = {{c1::\(289\)}}</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="str">
+        <f>cards_master!A53</f>
+        <v>square_18</v>
+      </c>
+      <c r="B52" t="str">
+        <f>cards_master!B53</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C52" t="str">
+        <f>"\("&amp;cards_master!C53&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D53&amp;"\)}}"</f>
+        <v>\(18^2\) = {{c1::\(324\)}}</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="str">
+        <f>cards_master!A54</f>
+        <v>square_19</v>
+      </c>
+      <c r="B53" t="str">
+        <f>cards_master!B54</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C53" t="str">
+        <f>"\("&amp;cards_master!C54&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D54&amp;"\)}}"</f>
+        <v>\(19^2\) = {{c1::\(361\)}}</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="str">
+        <f>cards_master!A55</f>
+        <v>square_20</v>
+      </c>
+      <c r="B54" t="str">
+        <f>cards_master!B55</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C54" t="str">
+        <f>"\("&amp;cards_master!C55&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D55&amp;"\)}}"</f>
+        <v>\(20^2\) = {{c1::\(400\)}}</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="str">
+        <f>cards_master!A56</f>
+        <v>sqrt_1</v>
+      </c>
+      <c r="B55" t="str">
+        <f>cards_master!B56</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C55" t="str">
+        <f>"\("&amp;cards_master!C56&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D56&amp;"\)}}"</f>
+        <v>\(sqrt(1)\) = {{c1::\(1\)}}</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="str">
+        <f>cards_master!A57</f>
+        <v>sqrt_2</v>
+      </c>
+      <c r="B56" t="str">
+        <f>cards_master!B57</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C56" t="str">
+        <f>"\("&amp;cards_master!C57&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D57&amp;"\)}}"</f>
+        <v>\(sqrt(4)\) = {{c1::\(2\)}}</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="str">
+        <f>cards_master!A58</f>
+        <v>sqrt_3</v>
+      </c>
+      <c r="B57" t="str">
+        <f>cards_master!B58</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C57" t="str">
+        <f>"\("&amp;cards_master!C58&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D58&amp;"\)}}"</f>
+        <v>\(sqrt(9)\) = {{c1::\(3\)}}</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="str">
+        <f>cards_master!A59</f>
+        <v>sqrt_4</v>
+      </c>
+      <c r="B58" t="str">
+        <f>cards_master!B59</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C58" t="str">
+        <f>"\("&amp;cards_master!C59&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D59&amp;"\)}}"</f>
+        <v>\(sqrt(16)\) = {{c1::\(4\)}}</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="str">
+        <f>cards_master!A60</f>
+        <v>sqrt_5</v>
+      </c>
+      <c r="B59" t="str">
+        <f>cards_master!B60</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C59" t="str">
+        <f>"\("&amp;cards_master!C60&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D60&amp;"\)}}"</f>
+        <v>\(sqrt(25)\) = {{c1::\(5\)}}</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="str">
+        <f>cards_master!A61</f>
+        <v>sqrt_6</v>
+      </c>
+      <c r="B60" t="str">
+        <f>cards_master!B61</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C60" t="str">
+        <f>"\("&amp;cards_master!C61&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D61&amp;"\)}}"</f>
+        <v>\(sqrt(36)\) = {{c1::\(6\)}}</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="str">
+        <f>cards_master!A62</f>
+        <v>sqrt_7</v>
+      </c>
+      <c r="B61" t="str">
+        <f>cards_master!B62</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C61" t="str">
+        <f>"\("&amp;cards_master!C62&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D62&amp;"\)}}"</f>
+        <v>\(sqrt(49)\) = {{c1::\(7\)}}</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="str">
+        <f>cards_master!A63</f>
+        <v>sqrt_8</v>
+      </c>
+      <c r="B62" t="str">
+        <f>cards_master!B63</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C62" t="str">
+        <f>"\("&amp;cards_master!C63&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D63&amp;"\)}}"</f>
+        <v>\(sqrt(64)\) = {{c1::\(8\)}}</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="str">
+        <f>cards_master!A64</f>
+        <v>sqrt_9</v>
+      </c>
+      <c r="B63" t="str">
+        <f>cards_master!B64</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C63" t="str">
+        <f>"\("&amp;cards_master!C64&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D64&amp;"\)}}"</f>
+        <v>\(sqrt(81)\) = {{c1::\(9\)}}</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="str">
+        <f>cards_master!A65</f>
+        <v>sqrt_10</v>
+      </c>
+      <c r="B64" t="str">
+        <f>cards_master!B65</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C64" t="str">
+        <f>"\("&amp;cards_master!C65&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D65&amp;"\)}}"</f>
+        <v>\(sqrt(100)\) = {{c1::\(10\)}}</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="str">
+        <f>cards_master!A66</f>
+        <v>sqrt_11</v>
+      </c>
+      <c r="B65" t="str">
+        <f>cards_master!B66</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C65" t="str">
+        <f>"\("&amp;cards_master!C66&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D66&amp;"\)}}"</f>
+        <v>\(sqrt(121)\) = {{c1::\(11\)}}</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="str">
+        <f>cards_master!A67</f>
+        <v>sqrt_12</v>
+      </c>
+      <c r="B66" t="str">
+        <f>cards_master!B67</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C66" t="str">
+        <f>"\("&amp;cards_master!C67&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D67&amp;"\)}}"</f>
+        <v>\(sqrt(144)\) = {{c1::\(12\)}}</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="str">
+        <f>cards_master!A68</f>
+        <v>sqrt_13</v>
+      </c>
+      <c r="B67" t="str">
+        <f>cards_master!B68</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C67" t="str">
+        <f>"\("&amp;cards_master!C68&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D68&amp;"\)}}"</f>
+        <v>\(sqrt(169)\) = {{c1::\(13\)}}</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="str">
+        <f>cards_master!A69</f>
+        <v>sqrt_14</v>
+      </c>
+      <c r="B68" t="str">
+        <f>cards_master!B69</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C68" t="str">
+        <f>"\("&amp;cards_master!C69&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D69&amp;"\)}}"</f>
+        <v>\(sqrt(196)\) = {{c1::\(14\)}}</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="str">
+        <f>cards_master!A70</f>
+        <v>sqrt_15</v>
+      </c>
+      <c r="B69" t="str">
+        <f>cards_master!B70</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C69" t="str">
+        <f>"\("&amp;cards_master!C70&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D70&amp;"\)}}"</f>
+        <v>\(sqrt(225)\) = {{c1::\(15\)}}</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="str">
+        <f>cards_master!A71</f>
+        <v>sqrt_16</v>
+      </c>
+      <c r="B70" t="str">
+        <f>cards_master!B71</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C70" t="str">
+        <f>"\("&amp;cards_master!C71&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D71&amp;"\)}}"</f>
+        <v>\(sqrt(256)\) = {{c1::\(16\)}}</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="str">
+        <f>cards_master!A72</f>
+        <v>sqrt_17</v>
+      </c>
+      <c r="B71" t="str">
+        <f>cards_master!B72</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C71" t="str">
+        <f>"\("&amp;cards_master!C72&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D72&amp;"\)}}"</f>
+        <v>\(sqrt(289)\) = {{c1::\(17\)}}</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="str">
+        <f>cards_master!A73</f>
+        <v>sqrt_18</v>
+      </c>
+      <c r="B72" t="str">
+        <f>cards_master!B73</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C72" t="str">
+        <f>"\("&amp;cards_master!C73&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D73&amp;"\)}}"</f>
+        <v>\(sqrt(324)\) = {{c1::\(18\)}}</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" t="str">
+        <f>cards_master!A74</f>
+        <v>sqrt_19</v>
+      </c>
+      <c r="B73" t="str">
+        <f>cards_master!B74</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C73" t="str">
+        <f>"\("&amp;cards_master!C74&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D74&amp;"\)}}"</f>
+        <v>\(sqrt(361)\) = {{c1::\(19\)}}</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="str">
+        <f>cards_master!A75</f>
+        <v>sqrt_20</v>
+      </c>
+      <c r="B74" t="str">
+        <f>cards_master!B75</f>
+        <v>squares and square roots</v>
+      </c>
+      <c r="C74" t="str">
+        <f>"\("&amp;cards_master!C75&amp;"\)"&amp;" = {{c1::"&amp;"\("&amp;cards_master!D75&amp;"\)}}"</f>
+        <v>\(sqrt(400)\) = {{c1::\(20\)}}</v>
       </c>
     </row>
   </sheetData>

--- a/excel/flashcards_master.xlsx
+++ b/excel/flashcards_master.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrmath3/Documents/GitHub/mr-sindel-math/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrmath3/Documents/GitHub/Math-Flashcards/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42A9ABFE-341E-2C47-AEBF-DD0838AA60A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1DA83C-24EF-1542-A3DD-41EDF101CDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{DB8C5BD4-B13A-AA46-9C13-196CEA47E358}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{DB8C5BD4-B13A-AA46-9C13-196CEA47E358}"/>
   </bookViews>
   <sheets>
     <sheet name="cards_master" sheetId="1" r:id="rId1"/>
-    <sheet name="anki_export" sheetId="2" r:id="rId2"/>
-    <sheet name="blooket_export" sheetId="3" r:id="rId3"/>
-    <sheet name="quizlet_export" sheetId="4" r:id="rId4"/>
-    <sheet name="gimkit_export" sheetId="5" r:id="rId5"/>
+    <sheet name="export" sheetId="6" r:id="rId2"/>
+    <sheet name="anki" sheetId="2" r:id="rId3"/>
+    <sheet name="blooket" sheetId="3" r:id="rId4"/>
+    <sheet name="quizlet" sheetId="4" r:id="rId5"/>
+    <sheet name="gimkit" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,8 +40,45 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="170">
   <si>
     <t>deck</t>
   </si>
@@ -538,6 +576,18 @@
   </si>
   <si>
     <t>squares and square roots</t>
+  </si>
+  <si>
+    <t>Topic:</t>
+  </si>
+  <si>
+    <t>Tab:</t>
+  </si>
+  <si>
+    <t>squares_and_roots</t>
+  </si>
+  <si>
+    <t>anki</t>
   </si>
 </sst>
 </file>
@@ -603,6 +653,64 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>13</v>
+    <v>3</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2678,6 +2786,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0112EA51-173F-CF4F-8FFE-3FD34720780F}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="e" cm="1" vm="1">
+        <f t="array" ref="A4">_xlfn._xlws.FILTER(anki!A:C,(cards_master!B:B=B2))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2891CE-84D5-EF44-9F8F-0E7C3321DDFA}">
   <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3865,7 +4005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73CA60E6-D3E8-4544-887C-6E9318034364}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3874,7 +4014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C35A34D1-7333-164B-A084-2BA53F3B571D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3883,7 +4023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4E6229-89EC-484C-B2E4-FE3173417D97}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
